--- a/vse-loti/340580437/spec-340580437.xlsx
+++ b/vse-loti/340580437/spec-340580437.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -82,15 +83,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -526,10 +529,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 3262-75, ст. 20</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 3262-75, ст. 20, Ду 25</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>25×3</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="n">
         <v>30</v>
       </c>
@@ -538,7 +545,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" s="4" t="n">
+        <v>0.07199999999999999</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
     </row>
@@ -548,10 +557,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 3262-75, ст. 20</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 3262-75, ст. 20, Ду 32</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>32×3</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="n">
         <v>30</v>
       </c>
@@ -560,7 +573,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" s="4" t="n">
+        <v>0.093</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -570,10 +585,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 3262-75, ст. 20</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 3262-75, ст. 20, Ду 40</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>40×4</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="n">
         <v>30</v>
       </c>
@@ -582,7 +601,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="4" t="n">
+        <v>0.13</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -592,10 +613,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В, Ду 57</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="n">
         <v>50</v>
       </c>
@@ -604,7 +629,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" s="4" t="n">
+        <v>0.262</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -614,10 +641,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В, Ду 76</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="n">
         <v>50</v>
       </c>
@@ -626,7 +657,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" s="4" t="n">
+        <v>0.355</v>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -636,10 +669,14 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В, Ду 89</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>89×6</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="n">
         <v>70</v>
       </c>
@@ -648,7 +685,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="4" t="n">
+        <v>0.86</v>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -658,10 +697,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В, Ду 108</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>108×6</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="n">
         <v>150</v>
       </c>
@@ -670,7 +713,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" s="4" t="n">
+        <v>2.264</v>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -680,10 +725,14 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В, Ду 159</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="n">
         <v>150</v>
       </c>
@@ -692,7 +741,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" s="4" t="n">
+        <v>3.396</v>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -702,10 +753,14 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В, Ду 273</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>273×8</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="n">
         <v>30</v>
       </c>
@@ -714,7 +769,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" s="4" t="n">
+        <v>1.568</v>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -724,10 +781,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В, Ду 325</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>325×8</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="n">
         <v>30</v>
       </c>
@@ -736,7 +797,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" s="4" t="n">
+        <v>1.876</v>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -746,10 +809,14 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В, Ду 377</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>377×10</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="n">
         <v>30</v>
       </c>
@@ -758,7 +825,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" s="4" t="n">
+        <v>2.715</v>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -768,10 +837,14 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 8732-78, ст. 20, группа В, Ду 426</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>426×10</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="n">
         <v>20</v>
       </c>
@@ -780,7 +853,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" s="4" t="n">
+        <v>2.052</v>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -790,10 +865,14 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 20295-85, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 20295-85, ст. 20, группа В, Ду 530</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>530×10</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="n">
         <v>20</v>
       </c>
@@ -802,7 +881,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" s="4" t="n">
+        <v>2.565</v>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -812,10 +893,14 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 20295-85, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 20295-85, ст. 20, группа В, Ду 630</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>630×10</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="n">
         <v>20</v>
       </c>
@@ -824,7 +909,9 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" s="4" t="n">
+        <v>3.058</v>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -834,10 +921,14 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная ГОСТ 20295-85, ст. 20, группа В</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Труба стальная ГОСТ 20295-85, ст. 20, группа В, Ду 720</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>720×11</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="n">
         <v>30</v>
       </c>
@@ -846,31 +937,37 @@
           <t>п.м</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" s="4" t="n">
+        <v>5.77</v>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
+      <c r="F17" s="6" t="n">
+        <v>27.036</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="7" t="n">
         <v>3424984.88</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Источник: Документация.docx</t>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Источник: Документация.docx
+ТЗ.docx</t>
         </is>
       </c>
     </row>
